--- a/shared/words/E6_单词汇总.xlsx
+++ b/shared/words/E6_单词汇总.xlsx
@@ -1186,6 +1186,11 @@
           <t>words/einheit6/zeigen.mp3</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zeig mir bitte dein Foto.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1208,6 +1213,11 @@
           <t>words/einheit6/ausziehen.mp3</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir ziehen nächste Woche aus.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1230,6 +1240,11 @@
           <t>words/einheit6/nehmen.mp3</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nimm bitte das Buch.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1279,6 +1294,11 @@
           <t>words/einheit6/umziehen.mp3</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In welches Zimmer möchtest du umziehen?</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1490,6 +1510,11 @@
           <t>words/einheit6/liegen.mp3</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Buch liegt auf dem Tisch.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1512,6 +1537,11 @@
           <t>words/einheit6/parken.mp3</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hier kann man nicht parken.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2025,6 +2055,11 @@
           <t>words/einheit6/Wand.mp3</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Nachttisch steht an der Wand.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2602,6 +2637,11 @@
           <t>words/einheit6/weg.mp3</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jetzt bin ich noch zu Hause, aber ich muss bald weg.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2624,6 +2664,11 @@
           <t>words/einheit6/nötig.mp3</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist nicht nötig.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2646,6 +2691,11 @@
           <t>words/einheit6/ziemlich.mp3</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist ziemlich teuer.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2668,6 +2718,11 @@
           <t>words/einheit6/zwar.mp3</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er ist zwar müde, aber er arbeitet weiter.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2690,6 +2745,11 @@
           <t>words/einheit6/hell.mp3</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Wohnzimmer ist hell.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2712,6 +2772,11 @@
           <t>words/einheit6/hoch.mp3</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Miete ist sehr hoch.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2734,6 +2799,11 @@
           <t>words/einheit6/fertig.mp3</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Hausaufgaben sind fertig.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2756,6 +2826,11 @@
           <t>words/einheit6/möglich.mp3</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ist das möglich?</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2778,6 +2853,11 @@
           <t>words/einheit6/da.mp3</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Da ist ein Taxi.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2800,6 +2880,11 @@
           <t>words/einheit6/schwach.mp3</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er ist noch sehr schwach.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2822,6 +2907,11 @@
           <t>words/einheit6/praktisch.mp3</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diese Tasche ist sehr praktisch.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2844,6 +2934,11 @@
           <t>words/einheit6/links.mp3</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Auto fährt mal links, mal rechts.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2893,6 +2988,11 @@
           <t>words/einheit6/warm.mp3</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heute ist es warm.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2913,6 +3013,11 @@
       <c r="F61" t="inlineStr">
         <is>
           <t>words/einheit6/modern.mp3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Jacke ist modern.</t>
         </is>
       </c>
     </row>
